--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484883_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484883_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0747</v>
+        <v>2.7908</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6721</v>
+        <v>2.2823</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4027</v>
+        <v>0.5085</v>
       </c>
       <c r="G2" t="n">
         <v>0.7118</v>
@@ -610,13 +610,13 @@
         <v>1.1322</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6272</v>
+        <v>0.3433</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5596</v>
+        <v>0.1698</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.1735</v>
       </c>
       <c r="V2" t="n">
         <v>1.547</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VALERO CHICA</t>
+          <t>A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7255</v>
+        <v>2.1685</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5536</v>
+        <v>1.2259</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1719</v>
+        <v>0.9427</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2795</v>
+        <v>1.4349</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0282</v>
+        <v>-1.2843</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2513</v>
+        <v>2.7191</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2756</v>
+        <v>2.3905</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1111</v>
+        <v>0.4077</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1645</v>
+        <v>1.9828</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0039</v>
+        <v>-0.9556</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0829</v>
+        <v>-1.6919</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0868</v>
+        <v>0.7363</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9435</v>
+        <v>1.5096</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4837</v>
+        <v>0.2058</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9763</v>
+        <v>-0.1829</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4926</v>
+        <v>0.3887</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9624</v>
+        <v>1.8488</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2452</v>
+        <v>1.8488</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. TERRADES DAROQUI</t>
+          <t>C. CAMPILLOS ALONSO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4666</v>
+        <v>1.8672</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8361</v>
+        <v>-0.2786</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6305</v>
+        <v>2.1458</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4349</v>
+        <v>1.3591</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2843</v>
+        <v>-0.277</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7191</v>
+        <v>1.6362</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3905</v>
+        <v>1.041</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4077</v>
+        <v>-0.227</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9828</v>
+        <v>1.268</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9556</v>
+        <v>0.3181</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6919</v>
+        <v>-0.0501</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7363</v>
+        <v>0.3682</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.3209</v>
+        <v>0.5661</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R4" t="n">
         <v>1.5096</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5038</v>
+        <v>-0.0581</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5726</v>
+        <v>-0.3761</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0765</v>
+        <v>0.3181</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8488</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8488</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SAEZ CALABUIG</t>
+          <t>J. VALERO CHICA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0164</v>
+        <v>1.8473</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.3888</v>
+        <v>1.3844</v>
       </c>
       <c r="F5" t="n">
-        <v>4.4051</v>
+        <v>0.4629</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2631</v>
+        <v>0.2795</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5987</v>
+        <v>0.0282</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3356</v>
+        <v>0.2513</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.0734</v>
+        <v>0.2756</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2139</v>
+        <v>0.1111</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1404</v>
+        <v>0.1645</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8103</v>
+        <v>0.0039</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6152</v>
+        <v>-0.0829</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1951</v>
+        <v>0.0868</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4531</v>
+        <v>0.9435</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0721</v>
+        <v>0.6055</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9304</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1417</v>
+        <v>-0.2016</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3587</v>
+        <v>0.9624</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3587</v>
+        <v>1.2452</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2828</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. CAMPILLOS ALONSO</t>
+          <t>O. GONZALEZ JURADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6013</v>
+        <v>1.5339</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5709</v>
+        <v>-0.1767</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1722</v>
+        <v>1.7106</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3591</v>
+        <v>-0.1109</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.277</v>
+        <v>-0.169</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6362</v>
+        <v>0.0582</v>
       </c>
       <c r="J6" t="n">
-        <v>1.041</v>
+        <v>-0.1579</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.227</v>
+        <v>0.4335</v>
       </c>
       <c r="L6" t="n">
-        <v>1.268</v>
+        <v>-0.5914</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3181</v>
+        <v>0.047</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0501</v>
+        <v>-0.6026</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3682</v>
+        <v>0.6496</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5661</v>
+        <v>1.5096</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>1.5096</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3239</v>
+        <v>0.1352</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6684</v>
+        <v>-0.0189</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3445</v>
+        <v>0.154</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. GONZALEZ JURADO</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2429</v>
+        <v>1.4938</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1767</v>
+        <v>-0.0031</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4196</v>
+        <v>1.4969</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1109</v>
+        <v>-0.1133</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.169</v>
+        <v>-0.4398</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0582</v>
+        <v>0.3265</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1579</v>
+        <v>0.1814</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4335</v>
+        <v>0.18</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5914</v>
+        <v>0.0015</v>
       </c>
       <c r="M7" t="n">
-        <v>0.047</v>
+        <v>-0.2947</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6026</v>
+        <v>-0.6198</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6496</v>
+        <v>0.325</v>
       </c>
       <c r="P7" t="n">
         <v>1.5096</v>
@@ -1000,28 +1000,28 @@
         <v>1.5096</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1558</v>
+        <v>0.0595</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0189</v>
+        <v>-0.1845</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.137</v>
+        <v>0.2441</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>A. SAEZ CALABUIG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4485</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0749</v>
+        <v>-3.3631</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5233</v>
+        <v>4.0612</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1133</v>
+        <v>-0.2631</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4398</v>
+        <v>-0.5987</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3265</v>
+        <v>0.3356</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1814</v>
+        <v>-1.0734</v>
       </c>
       <c r="K8" t="n">
-        <v>0.18</v>
+        <v>-1.2139</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0015</v>
+        <v>0.1404</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2947</v>
+        <v>0.8103</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6198</v>
+        <v>0.6152</v>
       </c>
       <c r="O8" t="n">
-        <v>0.325</v>
+        <v>0.1951</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5096</v>
+        <v>2.4531</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9858</v>
+        <v>0.7539</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2563</v>
+        <v>-0.0439</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2705</v>
+        <v>0.7978</v>
       </c>
       <c r="V8" t="n">
-        <v>0.038</v>
+        <v>-0.3587</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3587</v>
       </c>
       <c r="X8" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.428</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7874</v>
+        <v>-1.1771</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2154</v>
+        <v>1.2419</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8592</v>
@@ -1156,13 +1156,13 @@
         <v>1.887</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6454</v>
+        <v>0.2821</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1727</v>
+        <v>-0.217</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4727</v>
+        <v>0.4992</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2452</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6777</v>
+        <v>-3.0499</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4338</v>
+        <v>-2.044</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2439</v>
+        <v>-1.0059</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5447</v>
@@ -1234,13 +1234,13 @@
         <v>0.7548</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6425</v>
+        <v>-0.0147</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6343</v>
+        <v>-0.2446</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.2299</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3018</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6391</v>
+        <v>-4.7274</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.7519</v>
+        <v>-5.9725</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1128</v>
+        <v>1.2451</v>
       </c>
       <c r="G11" t="n">
         <v>-5.8019</v>
@@ -1312,13 +1312,13 @@
         <v>1.887</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3844</v>
+        <v>-0.4727</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3739</v>
+        <v>-0.5944</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0105</v>
+        <v>0.1218</v>
       </c>
       <c r="V11" t="n">
         <v>0.6036</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.687100000000002</v>
+        <v>4.687</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.1226</v>
+        <v>-8.1225</v>
       </c>
       <c r="F12" t="n">
-        <v>12.8096</v>
+        <v>12.8097</v>
       </c>
       <c r="G12" t="n">
         <v>-5.9078</v>
@@ -1360,7 +1360,7 @@
         <v>-6.338900000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4314</v>
+        <v>0.4313999999999991</v>
       </c>
       <c r="J12" t="n">
         <v>-5.782</v>
@@ -1393,10 +1393,10 @@
         <v>1.8398</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8853999999999999</v>
+        <v>-0.8855000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>2.7252</v>
+        <v>2.7255</v>
       </c>
       <c r="V12" t="n">
         <v>3.0941</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.1924</v>
+        <v>6.6809</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9671</v>
+        <v>3.3568</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2253</v>
+        <v>3.3241</v>
       </c>
       <c r="G13" t="n">
         <v>3.1506</v>
@@ -1468,13 +1468,13 @@
         <v>1.3209</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.305</v>
+        <v>0.1834</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8078</v>
+        <v>-0.4181</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5028</v>
+        <v>0.6015</v>
       </c>
       <c r="V13" t="n">
         <v>2.9695</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. ENGUIX TORMO</t>
+          <t>A. DOMINGUEZ CARRAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2335</v>
+        <v>1.5483</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.4046</v>
+        <v>-2.6472</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6381</v>
+        <v>4.1955</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5851</v>
+        <v>3.3004</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6777</v>
+        <v>1.4345</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9074</v>
+        <v>1.8659</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7851</v>
+        <v>1.7866</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1596</v>
+        <v>0.5924</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6254999999999999</v>
+        <v>1.1942</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8</v>
+        <v>1.5138</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5181</v>
+        <v>0.8421</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2819</v>
+        <v>0.6717</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5661</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.887</v>
+        <v>-3.774</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0182</v>
+        <v>0.2105</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0181</v>
+        <v>-0.6409</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0001</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1963</v>
+        <v>0.3018</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3208</v>
+        <v>-0.019</v>
       </c>
       <c r="X14" t="n">
-        <v>0.5171</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ CARRAL</t>
+          <t>H. ENGUIX TORMO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2162</v>
+        <v>1.4511</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.0369</v>
+        <v>-1.8918</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2531</v>
+        <v>3.3429</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3004</v>
+        <v>1.5851</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4345</v>
+        <v>0.6777</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8659</v>
+        <v>0.9074</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7866</v>
+        <v>0.7851</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5924</v>
+        <v>0.1596</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1942</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5138</v>
+        <v>0.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8421</v>
+        <v>0.5181</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6717</v>
+        <v>0.2819</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.2644</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.774</v>
+        <v>-1.887</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1216</v>
+        <v>0.2359</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0306</v>
+        <v>-0.469</v>
       </c>
       <c r="U15" t="n">
-        <v>0.909</v>
+        <v>0.7049</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3018</v>
+        <v>0.1963</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.019</v>
+        <v>-0.3208</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3208</v>
+        <v>0.5171</v>
       </c>
     </row>
     <row r="16">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3876</v>
+        <v>-1.1844</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8432</v>
+        <v>-2.1355</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4555</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5034</v>
@@ -1780,13 +1780,13 @@
         <v>0.9435</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1182</v>
+        <v>0.0851</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1611</v>
+        <v>-0.4534</v>
       </c>
       <c r="U17" t="n">
-        <v>0.043</v>
+        <v>0.5385</v>
       </c>
       <c r="V17" t="n">
         <v>-0.7661</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. LEMISHKA</t>
+          <t>J. ARTIGUES DANOBEITIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.454</v>
+        <v>-2.2267</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.5795</v>
+        <v>-0.2241</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1256</v>
+        <v>-2.0026</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.0549</v>
+        <v>-1.462</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3725</v>
+        <v>1.2506</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6823</v>
+        <v>-2.7126</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.0495</v>
+        <v>-1.661</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5009</v>
+        <v>1.4634</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.5486</v>
+        <v>-3.1244</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9946</v>
+        <v>0.199</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1284</v>
+        <v>-0.2128</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8663</v>
+        <v>0.4118</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.0192</v>
+        <v>0.7548</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.774</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.7548</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5066</v>
+        <v>-0.4516</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3195</v>
+        <v>-0.1101</v>
       </c>
       <c r="U18" t="n">
-        <v>1.187</v>
+        <v>-0.3415</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8865</v>
+        <v>-1.0679</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9244</v>
+        <v>1.547</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.8109</v>
+        <v>-2.6149</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0437</v>
+        <v>-2.8079</v>
       </c>
       <c r="E19" t="n">
         <v>-1.4753</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5684</v>
+        <v>-1.3327</v>
       </c>
       <c r="G19" t="n">
         <v>0.1631</v>
@@ -1936,13 +1936,13 @@
         <v>1.3209</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3656</v>
+        <v>-0.1299</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1488</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2169</v>
+        <v>0.0189</v>
       </c>
       <c r="V19" t="n">
         <v>-3.2185</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2904</v>
+        <v>-3.3275</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9572</v>
+        <v>-2.8598</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3331</v>
+        <v>-0.4677</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4251</v>
@@ -2014,13 +2014,13 @@
         <v>0.1887</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3992</v>
+        <v>0.362</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4703</v>
+        <v>-0.3729</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.7348</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6226</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ARTIGUES DANOBEITIA</t>
+          <t>V. LEMISHKA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0994</v>
+        <v>-4.5235</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.101</v>
+        <v>-5.3334</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9984</v>
+        <v>0.8099</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.462</v>
+        <v>-2.0549</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2506</v>
+        <v>-0.3725</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7126</v>
+        <v>-1.6823</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.661</v>
+        <v>-3.0495</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4634</v>
+        <v>-0.5009</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.1244</v>
+        <v>-2.5486</v>
       </c>
       <c r="M21" t="n">
-        <v>0.199</v>
+        <v>0.9946</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2128</v>
+        <v>0.1284</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4118</v>
+        <v>0.8663</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7548</v>
+        <v>-3.0192</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.774</v>
       </c>
       <c r="R21" t="n">
         <v>0.7548</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.3243</v>
+        <v>1.437</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9871</v>
+        <v>0.5657</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.3373</v>
+        <v>0.8713</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0679</v>
+        <v>-0.8865</v>
       </c>
       <c r="W21" t="n">
-        <v>1.547</v>
+        <v>0.9244</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.6149</v>
+        <v>-1.8109</v>
       </c>
     </row>
     <row r="22">
@@ -2125,25 +2125,25 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.015999999999999</v>
+        <v>-3.772700000000002</v>
       </c>
       <c r="E22" t="n">
-        <v>-11.8136</v>
+        <v>-12.5933</v>
       </c>
       <c r="F22" t="n">
-        <v>6.797700000000001</v>
+        <v>8.820500000000001</v>
       </c>
       <c r="G22" t="n">
         <v>4.370799999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>5.597099999999999</v>
+        <v>5.5971</v>
       </c>
       <c r="I22" t="n">
         <v>-1.2263</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3356999999999997</v>
+        <v>-0.3357000000000006</v>
       </c>
       <c r="K22" t="n">
         <v>2.6043</v>
@@ -2170,22 +2170,22 @@
         <v>8.114100000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6893000000000002</v>
+        <v>1.9324</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2681</v>
+        <v>-2.0475</v>
       </c>
       <c r="U22" t="n">
-        <v>1.9572</v>
+        <v>3.979699999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-3.094</v>
       </c>
       <c r="W22" t="n">
-        <v>4.8858</v>
+        <v>4.885800000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>-7.979800000000001</v>
+        <v>-7.9798</v>
       </c>
     </row>
   </sheetData>
